--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9388CD-F47E-4CB7-8890-71C6198F67F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7CD482-A7D2-4AE9-BB3B-39473C24F20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{55AABB10-9C92-4D0A-827C-A75C8CBFF77D}"/>
   </bookViews>
@@ -16,9 +16,12 @@
     <sheet name="config" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="footer">config!$B$15</definedName>
-    <definedName name="liste_regimes_tva">config!$E$18:$E$19</definedName>
-    <definedName name="table_config">config!$B$2:$B$15</definedName>
+    <definedName name="AAB">config!$B$20</definedName>
+    <definedName name="footer">config!$B$14</definedName>
+    <definedName name="liste_regimes_tva">config!$E$17:$E$18</definedName>
+    <definedName name="PMD">config!$B$18</definedName>
+    <definedName name="PMT">config!$B$19</definedName>
+    <definedName name="table_config">config!$B$2:$B$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>Dénomination sociale</t>
   </si>
@@ -80,14 +83,6 @@
   </si>
   <si>
     <t>RCS</t>
-  </si>
-  <si>
-    <t>Instructions de paiement</t>
-  </si>
-  <si>
-    <t>Tout retard de paiement engendre une pénalité exigible à compter de la date d'échéance. calculée sur la base de trois fois le taux d'intérêt légal. 
-Indemnité forfaitaire pour frais de recouvrement en cas de retard de paiement : 40 €.
-Les réglements reçus avant la date d'échéance ne donneront pas lieu à escompte.</t>
   </si>
   <si>
     <t>Informations entreprise</t>
@@ -155,6 +150,24 @@
   <si>
     <t>Ma société - SAS au capital de 10 000 EUR - RCS Paris B 123456789
 1 grande rue – contact@example.com - www.example.com  – N° TVA : FR01 123 456 789</t>
+  </si>
+  <si>
+    <t>Retard de paiement</t>
+  </si>
+  <si>
+    <t>Indemnité forfaitaire</t>
+  </si>
+  <si>
+    <t>Escompte</t>
+  </si>
+  <si>
+    <t>En cas de retard de paiement, des pénalités de retard au taux de 3 fois le taux d'intérêt légal seront exigibles (art. L441-10 du Code de commerce).</t>
+  </si>
+  <si>
+    <t>Une indemnité forfaitaire pour frais de recouvrement de 40 € sera due en cas de retard de paiement (art. L441-10 et D441-5 du Code de commerce).</t>
+  </si>
+  <si>
+    <t>Aucun escompte accordé pour paiement anticipé.</t>
   </si>
 </sst>
 </file>
@@ -373,7 +386,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -392,7 +405,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -417,11 +429,11 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -758,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4489C276-2268-4B1C-915C-859F7D5D5C2C}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -769,64 +781,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>16</v>
+      <c r="A1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>34</v>
+      <c r="B2" s="19" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>26</v>
+      <c r="B3" s="19" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>27</v>
+      <c r="B4" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B5" s="19"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>28</v>
+      <c r="B6" s="19" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>29</v>
+      <c r="B7" s="19" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
     </row>
@@ -834,117 +846,128 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>30</v>
+      <c r="B9" s="19" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>35</v>
+      <c r="B10" s="22" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>31</v>
+      <c r="B11" s="19" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>32</v>
+      <c r="B12" s="19" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="B13" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="D15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="21">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="23">
+        <v>23</v>
+      </c>
+      <c r="B17" s="21">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D17" s="12"/>
+      <c r="E17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="23">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D19" s="16"/>
-      <c r="E19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>23</v>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{6ADD858E-5B27-4AD9-9BF4-F26520A14BCC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15" xr:uid="{6ADD858E-5B27-4AD9-9BF4-F26520A14BCC}">
       <formula1>liste_regimes_tva</formula1>
     </dataValidation>
   </dataValidations>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7CD482-A7D2-4AE9-BB3B-39473C24F20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D430E35D-BB45-4EDC-B001-13BB7C685F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{55AABB10-9C92-4D0A-827C-A75C8CBFF77D}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Dénomination sociale</t>
   </si>
@@ -161,13 +161,19 @@
     <t>Escompte</t>
   </si>
   <si>
-    <t>En cas de retard de paiement, des pénalités de retard au taux de 3 fois le taux d'intérêt légal seront exigibles (art. L441-10 du Code de commerce).</t>
-  </si>
-  <si>
-    <t>Une indemnité forfaitaire pour frais de recouvrement de 40 € sera due en cas de retard de paiement (art. L441-10 et D441-5 du Code de commerce).</t>
-  </si>
-  <si>
-    <t>Aucun escompte accordé pour paiement anticipé.</t>
+    <t>Répertoire de sauvegarde json</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>En cas de retard de paiement, des pénalités de retard au taux de 3 fois le taux d'intérêt légal seront exigibles (art. L441-10 du Code de commerce)</t>
+  </si>
+  <si>
+    <t>Une indemnité forfaitaire pour frais de recouvrement de 40 € sera due en cas de retard de paiement (art. L441-10 et D441-5 du Code de commerce)</t>
+  </si>
+  <si>
+    <t>Aucun escompte accordé pour paiement anticipé</t>
   </si>
 </sst>
 </file>
@@ -770,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4489C276-2268-4B1C-915C-859F7D5D5C2C}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -939,7 +945,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="16" t="s">
@@ -954,7 +960,7 @@
         <v>36</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -962,7 +968,15 @@
         <v>37</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D430E35D-BB45-4EDC-B001-13BB7C685F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D639EE8B-7886-4E23-B4D0-AB33647B917E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{55AABB10-9C92-4D0A-827C-A75C8CBFF77D}"/>
   </bookViews>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D639EE8B-7886-4E23-B4D0-AB33647B917E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B1EFAD-6038-4E65-87A5-4845E2CF8227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{55AABB10-9C92-4D0A-827C-A75C8CBFF77D}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="AAB">config!$B$20</definedName>
     <definedName name="footer">config!$B$14</definedName>
-    <definedName name="liste_regimes_tva">config!$E$17:$E$18</definedName>
+    <definedName name="liste_regimes_tva">config!$E$17:$E$19</definedName>
     <definedName name="PMD">config!$B$18</definedName>
     <definedName name="PMT">config!$B$19</definedName>
     <definedName name="table_config">config!$B$2:$B$14</definedName>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Dénomination sociale</t>
   </si>
@@ -174,13 +174,19 @@
   </si>
   <si>
     <t>Aucun escompte accordé pour paiement anticipé</t>
+  </si>
+  <si>
+    <t>Franchise en base de TVA (art. 293 B)</t>
+  </si>
+  <si>
+    <t>Micro-entreprises</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +267,13 @@
     <font>
       <sz val="11"/>
       <color theme="3" tint="0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -425,11 +438,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -440,6 +448,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -790,7 +801,7 @@
       <c r="A1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>14</v>
       </c>
     </row>
@@ -798,7 +809,7 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>32</v>
       </c>
     </row>
@@ -806,7 +817,7 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="16" t="s">
         <v>24</v>
       </c>
     </row>
@@ -814,7 +825,7 @@
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="17" t="s">
         <v>25</v>
       </c>
     </row>
@@ -822,13 +833,13 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="19"/>
+      <c r="B5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -836,7 +847,7 @@
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>27</v>
       </c>
     </row>
@@ -844,7 +855,7 @@
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -852,7 +863,7 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -860,7 +871,7 @@
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>33</v>
       </c>
     </row>
@@ -868,7 +879,7 @@
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -876,7 +887,7 @@
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -884,7 +895,7 @@
       <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="16" t="s">
         <v>31</v>
       </c>
     </row>
@@ -892,7 +903,7 @@
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="17" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="6"/>
@@ -903,7 +914,7 @@
       <c r="A15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="18" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="9" t="s">
@@ -916,7 +927,7 @@
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="18">
         <v>1</v>
       </c>
       <c r="D16" s="12" t="s">
@@ -929,7 +940,7 @@
       <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="18">
         <v>1</v>
       </c>
       <c r="D17" s="12"/>
@@ -944,14 +955,14 @@
       <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -959,15 +970,22 @@
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="20" t="s">
         <v>41</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -975,7 +993,7 @@
       <c r="A21" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="20" t="s">
         <v>39</v>
       </c>
     </row>
